--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\murty.govindusridhar\Documents\UiPath\qm_oca_salesforce\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cronosnet-my.sharepoint.com/personal/d_engemann_cronos_de/Documents/Desktop/Kunden/Olympus/sam_qm_oca_FrameWork/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C629EC-68A5-4825-9C1C-1A8219DFD5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="630" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -292,7 +292,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -308,9 +308,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -348,7 +348,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -454,7 +454,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -605,7 +605,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="43.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.140625" bestFit="1" customWidth="1"/>
@@ -1763,7 +1763,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Z988"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="41" customWidth="1"/>
     <col min="2" max="2" width="51" customWidth="1"/>
@@ -2921,7 +2921,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="30.140625" customWidth="1"/>
